--- a/docs/Salary Calculations.xlsx
+++ b/docs/Salary Calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\hrportal\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D25B39-C9C2-49EC-95D3-2C21E4D7100C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E59489-89D1-41D2-BFB4-0D8D964EB04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47910" yWindow="0" windowWidth="19380" windowHeight="10530" xr2:uid="{461494F0-5780-47EA-B1B9-BB98E395037F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{461494F0-5780-47EA-B1B9-BB98E395037F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="62">
   <si>
     <t>layla</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>wd</t>
+  </si>
+  <si>
+    <t>September End</t>
+  </si>
+  <si>
+    <t>October First</t>
   </si>
 </sst>
 </file>
@@ -599,37 +605,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068B6A2D-3AC9-4114-8B39-1D0D1002F4FE}">
-  <dimension ref="B2:X59"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:AB59"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.59765625" customWidth="1"/>
-    <col min="6" max="6" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.9296875" customWidth="1"/>
-    <col min="10" max="10" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" customWidth="1"/>
-    <col min="12" max="12" width="43.73046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.796875" customWidth="1"/>
-    <col min="14" max="14" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="43.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.33203125" customWidth="1"/>
-    <col min="18" max="18" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="43.73046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.06640625" customWidth="1"/>
-    <col min="22" max="22" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.6328125" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.90625" customWidth="1"/>
+    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.36328125" customWidth="1"/>
+    <col min="12" max="12" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.81640625" customWidth="1"/>
+    <col min="14" max="14" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.36328125" customWidth="1"/>
+    <col min="18" max="18" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.08984375" customWidth="1"/>
+    <col min="22" max="22" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.36328125" customWidth="1"/>
+    <col min="26" max="26" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="44.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:28" x14ac:dyDescent="0.35">
       <c r="H2" s="3"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B4" s="7" t="s">
         <v>52</v>
       </c>
@@ -685,8 +694,17 @@
       <c r="X4" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -723,8 +741,14 @@
       <c r="W5" s="3">
         <v>46054</v>
       </c>
-    </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
@@ -761,8 +785,14 @@
       <c r="W6" s="3">
         <v>46081</v>
       </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -818,8 +848,17 @@
       <c r="X7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>46298</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -875,8 +914,17 @@
       <c r="X8" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>46305</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B9" s="7" t="s">
         <v>28</v>
       </c>
@@ -932,8 +980,17 @@
       <c r="X9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -995,8 +1052,18 @@
       <c r="X10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="5">
+        <f>NETWORKDAYS.INTL(AA5,AA7-1,"0000100")</f>
+        <v>1</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1058,8 +1125,18 @@
       <c r="X11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>NETWORKDAYS.INTL(AA7,AA8,"0000100")</f>
+        <v>7</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -1121,8 +1198,18 @@
       <c r="X12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA12" s="5">
+        <f>IF(OR(AA8=AA6,AA8&gt;AA6),0,NETWORKDAYS.INTL(AA8+1,AA6,"0000100"))</f>
+        <v>18</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -1159,8 +1246,14 @@
       <c r="W13">
         <v>1800</v>
       </c>
-    </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA13">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1216,8 +1309,17 @@
       <c r="X14" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA14">
+        <v>70</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>9</v>
       </c>
@@ -1260,8 +1362,15 @@
         <f>W13/26</f>
         <v>69.230769230769226</v>
       </c>
-    </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z15" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15">
+        <f>AA13/26</f>
+        <v>57.692307692307693</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>10</v>
       </c>
@@ -1304,8 +1413,15 @@
         <f>W14/26</f>
         <v>11.538461538461538</v>
       </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z16" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA16">
+        <f>AA14/26</f>
+        <v>2.6923076923076925</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -1366,8 +1482,18 @@
       <c r="X17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA17">
+        <f>AA10*(AA13+AA14)/26</f>
+        <v>60.384615384615387</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>18</v>
       </c>
@@ -1428,8 +1554,18 @@
       <c r="X18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA18">
+        <f>AA13/26*AA11</f>
+        <v>403.84615384615387</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1626,17 @@
       <c r="X19" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA19">
+        <v>100</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>21</v>
       </c>
@@ -1552,8 +1697,18 @@
       <c r="X20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA20">
+        <f>AA12/26*(AA13+AA14)</f>
+        <v>1086.9230769230769</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>22</v>
       </c>
@@ -1614,8 +1769,18 @@
       <c r="X21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Z21" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA21">
+        <f>-IF(ISNUMBER(SEARCH("Kuwaiti",Z4)),AA13*11.5%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -1676,8 +1841,18 @@
       <c r="X22" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA22" s="2">
+        <f>AA17+AA18+AA19</f>
+        <v>564.23076923076928</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
@@ -1720,8 +1895,15 @@
         <f>W17</f>
         <v>484.61538461538464</v>
       </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA23">
+        <f>AA17</f>
+        <v>60.384615384615387</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>24</v>
       </c>
@@ -1764,8 +1946,15 @@
         <f>W18</f>
         <v>346.15384615384613</v>
       </c>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA24">
+        <f>AA18</f>
+        <v>403.84615384615387</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>35</v>
       </c>
@@ -1808,8 +1997,15 @@
         <f>W19</f>
         <v>57.692307692307693</v>
       </c>
-    </row>
-    <row r="26" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Z25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA25">
+        <f>AA19</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
@@ -1852,8 +2048,15 @@
         <f>W20+W21</f>
         <v>1050</v>
       </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA26" s="2">
+        <f>AA20+AA21</f>
+        <v>1086.9230769230769</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
@@ -1896,8 +2099,15 @@
         <f>W20</f>
         <v>1050</v>
       </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA27">
+        <f>AA20</f>
+        <v>1086.9230769230769</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
@@ -1940,8 +2150,15 @@
         <f>W21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Z28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA28">
+        <f>AA21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="9" t="s">
         <v>58</v>
       </c>
@@ -1984,8 +2201,15 @@
         <f>W26+W22</f>
         <v>1938.4615384615386</v>
       </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="Z29" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA29" s="2">
+        <f>AA26+AA22</f>
+        <v>1651.1538461538462</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.35">
       <c r="C30">
         <f>C29+1158.371</f>
         <v>4261.1402307692306</v>
@@ -1993,16 +2217,16 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:28" x14ac:dyDescent="0.35">
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="V31" s="6"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:28" x14ac:dyDescent="0.35">
       <c r="O32" s="4"/>
       <c r="V32" s="6"/>
     </row>
-    <row r="34" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F34" s="2" t="s">
         <v>52</v>
       </c>
@@ -2013,7 +2237,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F35" t="s">
         <v>13</v>
       </c>
@@ -2021,7 +2245,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="36" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F36" t="s">
         <v>26</v>
       </c>
@@ -2029,7 +2253,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="37" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F37" t="s">
         <v>5</v>
       </c>
@@ -2040,7 +2264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F38" t="s">
         <v>6</v>
       </c>
@@ -2051,7 +2275,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F39" s="3" t="s">
         <v>28</v>
       </c>
@@ -2062,7 +2286,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F40" t="s">
         <v>11</v>
       </c>
@@ -2074,7 +2298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F41" t="s">
         <v>19</v>
       </c>
@@ -2086,7 +2310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F42" t="s">
         <v>14</v>
       </c>
@@ -2102,7 +2326,7 @@
         <v>4041.3461538461543</v>
       </c>
     </row>
-    <row r="43" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F43" t="s">
         <v>7</v>
       </c>
@@ -2110,7 +2334,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="44" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F44" t="s">
         <v>8</v>
       </c>
@@ -2121,7 +2345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F45" t="s">
         <v>9</v>
       </c>
@@ -2134,7 +2358,7 @@
         <v>326.92307692307691</v>
       </c>
     </row>
-    <row r="46" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F46" t="s">
         <v>10</v>
       </c>
@@ -2143,7 +2367,7 @@
         <v>38.46153846153846</v>
       </c>
     </row>
-    <row r="47" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F47" t="s">
         <v>17</v>
       </c>
@@ -2155,7 +2379,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F48" t="s">
         <v>18</v>
       </c>
@@ -2167,7 +2391,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F49" t="s">
         <v>20</v>
       </c>
@@ -2179,7 +2403,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F50" t="s">
         <v>21</v>
       </c>
@@ -2191,7 +2415,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F51" t="s">
         <v>22</v>
       </c>
@@ -2203,7 +2427,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F52" s="2" t="s">
         <v>56</v>
       </c>
@@ -2215,7 +2439,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F53" s="6" t="s">
         <v>57</v>
       </c>
@@ -2224,7 +2448,7 @@
         <v>5884.6153846153848</v>
       </c>
     </row>
-    <row r="54" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F54" s="6" t="s">
         <v>24</v>
       </c>
@@ -2233,7 +2457,7 @@
         <v>5192.3076923076924</v>
       </c>
     </row>
-    <row r="55" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F55" s="6" t="s">
         <v>35</v>
       </c>
@@ -2242,7 +2466,7 @@
         <v>692.30769230769226</v>
       </c>
     </row>
-    <row r="56" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F56" s="9" t="s">
         <v>55</v>
       </c>
@@ -2252,7 +2476,7 @@
       </c>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F57" s="6" t="s">
         <v>25</v>
       </c>
@@ -2261,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F58" s="6" t="s">
         <v>22</v>
       </c>
@@ -2270,7 +2494,7 @@
         <v>-862.5</v>
       </c>
     </row>
-    <row r="59" spans="6:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F59" s="9" t="s">
         <v>58</v>
       </c>
@@ -2288,9 +2512,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613003AF-99E8-4755-82B3-8F369EFACA3A}">
   <dimension ref="B8:I19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>3500</v>
       </c>
@@ -2313,7 +2537,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>1266.9680000000001</v>
       </c>
@@ -2336,37 +2560,37 @@
         <v>1158.3710000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10">
-        <f>B9/B8</f>
+        <f t="shared" ref="B10:H10" si="0">B9/B8</f>
         <v>0.36199085714285717</v>
       </c>
       <c r="C10">
-        <f>C9/C8</f>
+        <f t="shared" si="0"/>
         <v>0.36199093333333332</v>
       </c>
       <c r="D10">
-        <f>D9/D8</f>
+        <f t="shared" si="0"/>
         <v>0.36199083333333332</v>
       </c>
       <c r="E10">
-        <f>E9/E8</f>
+        <f t="shared" si="0"/>
         <v>0.36199090909090909</v>
       </c>
       <c r="F10">
-        <f>F9/F8</f>
+        <f t="shared" si="0"/>
         <v>0.3619911111111111</v>
       </c>
       <c r="G10">
-        <f>G9/G8</f>
+        <f t="shared" si="0"/>
         <v>0.36199066666666668</v>
       </c>
       <c r="H10">
-        <f>H9/H8</f>
+        <f t="shared" si="0"/>
         <v>0.36199093750000005</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="H16">
         <v>24</v>
       </c>
@@ -2374,19 +2598,19 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H17">
         <f>1500*24/26</f>
         <v>1384.6153846153845</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H18">
         <f>100*24/26</f>
         <v>92.307692307692307</v>
       </c>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H19">
         <f>70*24/26</f>
         <v>64.615384615384613</v>
